--- a/sampleprojects/TaxReturn/excel/states/UT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/UT.xlsx
@@ -72,7 +72,7 @@
     <t>UT taxable income = max(AGI − dependent_exemption × #dependents, 0); tax = 4.5% × taxable_income</t>
   </si>
   <si>
-    <t>set result.ut_taxable_income = the maximum of (result.agi - length of job.dependents * ut_personal_exemption) and 0.0; set result.ut_tax = result.ut_taxable_income * ut_tax_rate; set result.ut_state_tax = result.ut_tax; add "  UT taxable income (AGI - $2,111 per dependent): $" + result.ut_taxable_income to job.audit_trail; add "  UT state tax (4.5%): $" + result.ut_state_tax to job.audit_trail</t>
+    <t>set result.ut_taxable_income = the maximum of (result.state_calc_agi - length of job.dependents * ut_personal_exemption) and 0.0; set result.ut_tax = result.ut_taxable_income * ut_tax_rate; set result.ut_state_tax = result.ut_tax; add "  UT taxable income (AGI - $2,111 per dependent): $" + result.ut_taxable_income to job.audit_trail; add "  UT state tax (4.5%): $" + result.ut_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>

--- a/sampleprojects/TaxReturn/excel/states/UT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/UT.xlsx
@@ -72,7 +72,7 @@
     <t>UT taxable income = max(AGI − dependent_exemption × #dependents, 0); tax = 4.5% × taxable_income</t>
   </si>
   <si>
-    <t>set result.ut_taxable_income = the maximum of (result.state_calc_agi - length of job.dependents * ut_personal_exemption) and 0.0; set result.ut_tax = result.ut_taxable_income * ut_tax_rate; set result.ut_state_tax = result.ut_tax; add "  UT taxable income (AGI - $2,111 per dependent): $" + result.ut_taxable_income to job.audit_trail; add "  UT state tax (4.5%): $" + result.ut_state_tax to job.audit_trail</t>
+    <t>set result.ut_taxable_income = the maximum of (result.state_calc_agi - length of job.dependents * ut_personal_exemption) and 0.0; set result.ut_tax = result.ut_taxable_income * ut_tax_rate; set result.ut_state_tax = result.ut_tax; add "  UT taxable income (AGI - $2,111 per dependent): $" + result.ut_taxable_income to job.audit_trail; add "  UT state tax (4.5%): $" + result.ut_state_tax to job.audit_trail; set result.computed_state_taxable_income = result.ut_taxable_income; set result.computed_state_tax = result.ut_state_tax</t>
   </si>
   <si>
     <t>X</t>

--- a/sampleprojects/TaxReturn/excel/states/UT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/UT.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="ut tax" sheetId="2" r:id="rId4"/>
-    <sheet name="UT Military Retirement Exclusio" sheetId="3" r:id="rId6"/>
+    <sheet name="UT Military Retirement Credit" sheetId="3" r:id="rId6"/>
     <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>DT: ut tax</t>
   </si>
@@ -45,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.ut_tax = 0; set result.ut_state_tax = 0; set result.ut_taxable_income = 0; add "  Utah Tax Calculation (Form TC-40) - flat 4.5%" to job.audit_trail</t>
+    <t>set result.ut_tax = 0; set result.ut_state_tax = 0; set result.ut_taxable_income = 0; set result.ut_base_tax = 0; set result.ut_taxpayer_credit = 0; set result.ut_military_retirement_credit = 0.0; perform UT_Military_Retirement_Credit; set result.ut_taxable_income = the maximum of result.state_calc_agi and 0.0; set result.ut_base_tax = result.ut_taxable_income * ut_tax_rate; add "  Utah Tax Calculation (Form TC-40, 2025) - 4.5% less the taxpayer tax credit and the military retirement credit" to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -54,195 +54,237 @@
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Always compute (UT has no filing-status differences in rate)</t>
+    <t>Married filing jointly or surviving spouse: $36,426 phase-out base</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFJ" or job.filing_status is equal to "QSS"</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Head of household: $27,320 phase-out base</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "HOH"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ACTIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: ACTIONS</t>
+  </si>
+  <si>
+    <t>TC-40 lines 11-20: 6% of (dependent exemptions + federal deduction) less 1.3% of taxable income over $36,426</t>
+  </si>
+  <si>
+    <t>set result.ut_taxpayer_credit = the maximum of ((length of job.dependents * ut_personal_exemption + result.total_deduction) * ut_taxpayer_credit_rate - (the maximum of (result.ut_taxable_income - ut_credit_phaseout_joint) and 0.0) * ut_credit_phaseout_rate) and 0.0</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>TC-40 lines 11-20, head of household base $27,320</t>
+  </si>
+  <si>
+    <t>set result.ut_taxpayer_credit = the maximum of ((length of job.dependents * ut_personal_exemption + result.total_deduction) * ut_taxpayer_credit_rate - (the maximum of (result.ut_taxable_income - ut_credit_phaseout_hoh) and 0.0) * ut_credit_phaseout_rate) and 0.0</t>
+  </si>
+  <si>
+    <t>TC-40 lines 11-20, single/MFS base $18,213</t>
+  </si>
+  <si>
+    <t>set result.ut_taxpayer_credit = the maximum of ((length of job.dependents * ut_personal_exemption + result.total_deduction) * ut_taxpayer_credit_rate - (the maximum of (result.ut_taxable_income - ut_credit_phaseout_single) and 0.0) * ut_credit_phaseout_rate) and 0.0</t>
+  </si>
+  <si>
+    <t>TC-40 line 22 tax less the taxpayer tax credit, line 24 less the military retirement credit (code AJ), not below zero</t>
+  </si>
+  <si>
+    <t>set result.ut_tax = the maximum of (result.ut_base_tax - result.ut_taxpayer_credit - result.ut_military_retirement_credit) and 0.0; set result.ut_state_tax = result.ut_tax; set result.computed_state_taxable_income = result.ut_taxable_income; set result.computed_state_tax = result.ut_tax; add "  UT tax 4.5% of $" + result.ut_taxable_income + " = $" + result.ut_base_tax + "; taxpayer tax credit $" + result.ut_taxpayer_credit + "; military retirement credit $" + result.ut_military_retirement_credit + "; tax $" + result.ut_tax to job.audit_trail</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Utah MFJ/QSS (2025 TC-40): 4.5% of Utah taxable income (federal AGI; the standard deduction and exemptions are not subtracted), less the taxpayer tax credit (6% of the federal deduction plus $2,111 per dependent, phased out at 1.3% of taxable income over $36,426) and the military retirement credit (4.5% of military retirement pay, code AJ).</t>
+  </si>
+  <si>
+    <t>Utah HOH: as above with the $27,320 phase-out base.</t>
+  </si>
+  <si>
+    <t>Utah Single/MFS (2025 TC-40 lines 9-25): 4.5% of taxable income, less the taxpayer tax credit (6% of the federal deduction plus dependent exemptions, less 1.3% of taxable income over $18,213; Utah Code 59-10-1018) and the military retirement credit (Utah Code 59-10-1043).</t>
+  </si>
+  <si>
+    <t>DT: UT Military Retirement Credit</t>
+  </si>
+  <si>
+    <t>COMMENTS: Utah military retirement exclusion. Skeleton — see issue #446. UT allows up to $10,000 exemption on military retirement pay with income caps ($50k Single / $65k MFJ AGI); must choose between military retirement or Social Security exemption.</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 42301</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retirement pay included in AGI</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>TC-40A Part 3 code AJ worksheet: taxable military retirement pay times 0.045 (Utah Code 59-10-1043)</t>
+  </si>
+  <si>
+    <t>add taxpayer.military_retirement_pay * ut_tax_rate to result.ut_military_retirement_credit</t>
+  </si>
+  <si>
+    <t>Military retirement credit, TC-40A Part 3 code AJ: 4.5% of military retirement pay included in AGI, nonrefundable, no carryforward, not with the retirement credit code 18 (Utah Code 59-10-1043; 2025 TC-40 instructions p. 21-22). Utah has no exemption for the pay itself.</t>
+  </si>
+  <si>
+    <t>No military retirement pay for this taxpayer.</t>
+  </si>
+  <si>
+    <t>EDD: EDD</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SubType</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Q Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>(16 attributes)</t>
+  </si>
+  <si>
+    <t>ut_base_tax</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>UT base tax before taxpayer credit (computed)</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_hoh</t>
+  </si>
+  <si>
+    <t>27320.0</t>
+  </si>
+  <si>
+    <t>UT taxpayer tax credit phase-out base, head of household: $27,320 for 2025, 1.5 times the single base as every year (TC-40 line 17). Derived from the single figure, not read from the 2025 instructions; confirm when a HOH Utah scenario is written.</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_joint</t>
+  </si>
+  <si>
+    <t>36426.0</t>
+  </si>
+  <si>
+    <t>UT taxpayer tax credit phase-out base, married filing jointly or surviving spouse: $36,426 for 2025, twice the single base as every year (TC-40 line 17). Derived from the single figure, not read from the 2025 instructions; confirm when a joint Utah scenario is written.</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_rate</t>
+  </si>
+  <si>
+    <t>0.013</t>
+  </si>
+  <si>
+    <t>UT taxpayer credit phase-out rate 1.3% (2025)</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_single</t>
+  </si>
+  <si>
+    <t>18213.0</t>
+  </si>
+  <si>
+    <t>UT taxpayer tax credit phase-out base, single: $18,213 for 2025 (TC-40 line 17; 2025 TC-40 instructions). The credit is reduced by 1.3% of Utah taxable income over this amount.</t>
+  </si>
+  <si>
+    <t>ut_military_retirement_credit</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Utah military retirement credit (computed per taxpayer by UT_Military_Retirement_Credit): a nonrefundable credit of 4.5% (the tax rate) of military retirement pay included in AGI, TC-40A Part 3 code AJ, Utah Code 59-10-1043; cannot be claimed with the retirement credit, code 18 (2025 TC-40 instructions p. 21-22). Utah has no exemption or AGI cap for the pay itself (#1330).</t>
+  </si>
+  <si>
+    <t>ut_military_retirement_taxable</t>
+  </si>
+  <si>
+    <t>UT taxable military retirement after exemption (computed)</t>
+  </si>
+  <si>
+    <t>ut_personal_exemption</t>
+  </si>
+  <si>
+    <t>2111.0</t>
+  </si>
+  <si>
+    <t>UT personal exemption $2,111 per dependent for 2025 (TC-40 line 11; Utah Code 59-10-1018(1)(g)). It is a component of the taxpayer tax credit, not a deduction from taxable income.</t>
+  </si>
+  <si>
+    <t>ut_social_security_exempt</t>
+  </si>
+  <si>
+    <t>boolean</t>
   </si>
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>ACTIONS: COMMENTS</t>
-  </si>
-  <si>
-    <t>DSL: ACTIONS</t>
-  </si>
-  <si>
-    <t>UT taxable income = max(AGI − dependent_exemption × #dependents, 0); tax = 4.5% × taxable_income</t>
-  </si>
-  <si>
-    <t>set result.ut_taxable_income = the maximum of (result.state_calc_agi - length of job.dependents * ut_personal_exemption) and 0.0; set result.ut_tax = result.ut_taxable_income * ut_tax_rate; set result.ut_state_tax = result.ut_tax; add "  UT taxable income (AGI - $2,111 per dependent): $" + result.ut_taxable_income to job.audit_trail; add "  UT state tax (4.5%): $" + result.ut_state_tax to job.audit_trail; set result.computed_state_taxable_income = result.ut_taxable_income; set result.computed_state_tax = result.ut_state_tax</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Policy:</t>
-  </si>
-  <si>
-    <t>Policy Statements</t>
-  </si>
-  <si>
-    <t>UT flat tax: 4.5% × max(AGI − $2,111 × #dependents, 0)</t>
-  </si>
-  <si>
-    <t>DT: UT Military Retirement Exclusion</t>
-  </si>
-  <si>
-    <t>COMMENTS: Utah military retirement exclusion. Skeleton — see issue #446. UT allows up to $10,000 exemption on military retirement pay with income caps ($50k Single / $65k MFJ AGI); must choose between military retirement or Social Security exemption.</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 42301</t>
-  </si>
-  <si>
-    <t>EDD: EDD</t>
-  </si>
-  <si>
-    <t>Entity</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>SubType</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Access</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Collect</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Q Type</t>
-  </si>
-  <si>
-    <t>Options</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(18 attributes)</t>
-  </si>
-  <si>
-    <t>ut_base_tax</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>UT base tax before taxpayer credit (computed)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_hoh</t>
-  </si>
-  <si>
-    <t>23844.0</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out threshold head of household (2025)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_joint</t>
-  </si>
-  <si>
-    <t>31792.0</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out threshold married filing jointly (2025)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_rate</t>
-  </si>
-  <si>
-    <t>0.013</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out rate 1.3% (2025)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_single</t>
-  </si>
-  <si>
-    <t>15896.0</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out threshold single (2025). Source: Utah State Tax Commission</t>
-  </si>
-  <si>
-    <t>ut_military_exemption_agi_cap_joint</t>
-  </si>
-  <si>
-    <t>65000.0</t>
-  </si>
-  <si>
-    <t>UT military retirement exemption AGI cap joint (2025). Source: MOAA State Report Card</t>
-  </si>
-  <si>
-    <t>ut_military_exemption_agi_cap_single</t>
-  </si>
-  <si>
-    <t>50000.0</t>
-  </si>
-  <si>
-    <t>UT military retirement exemption AGI cap single (2025). Source: MOAA State Report Card</t>
-  </si>
-  <si>
-    <t>ut_military_retirement_exemption</t>
-  </si>
-  <si>
-    <t>10000.0</t>
-  </si>
-  <si>
-    <t>UT military retirement exemption amount (2025). Must choose between this or SS exemption. Source: MOAA State Report Card</t>
-  </si>
-  <si>
-    <t>ut_military_retirement_taxable</t>
-  </si>
-  <si>
-    <t>UT taxable military retirement after exemption (computed)</t>
-  </si>
-  <si>
-    <t>ut_personal_exemption</t>
-  </si>
-  <si>
-    <t>2111.0</t>
-  </si>
-  <si>
-    <t>UT personal exemption per dependent (2025). Source: Utah State Tax Commission</t>
-  </si>
-  <si>
-    <t>ut_social_security_exempt</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
     <t>UT fully exempts Social Security benefits from state income tax (2025). Source: Utah State Tax Commission</t>
   </si>
   <si>
@@ -255,9 +297,6 @@
     <t>ut_state_tax</t>
   </si>
   <si>
-    <t>rw</t>
-  </si>
-  <si>
     <t>UT state income tax (alias for ut_tax)</t>
   </si>
   <si>
@@ -285,7 +324,7 @@
     <t>ut_taxpayer_credit</t>
   </si>
   <si>
-    <t>UT taxpayer tax credit amount (computed)</t>
+    <t>UT taxpayer tax credit (computed): 6% of (federal deduction + $2,111 per dependent), reduced by 1.3% of Utah taxable income over the filing-status base, not below zero (TC-40 lines 11-20; Utah Code 59-10-1018).</t>
   </si>
   <si>
     <t>ut_taxpayer_credit_rate</t>
@@ -988,10 +1027,10 @@
         <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>8</v>
@@ -1033,235 +1072,589 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
         <v>16</v>
       </c>
-      <c r="D14" s="4">
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
-        <v>3</v>
-      </c>
-      <c r="G14" s="4">
-        <v>4</v>
-      </c>
-      <c r="H14" s="4">
-        <v>5</v>
-      </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
-        <v>7</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
-        <v>9</v>
-      </c>
-      <c r="M14" s="4">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4">
-        <v>11</v>
-      </c>
-      <c r="O14" s="4">
-        <v>12</v>
-      </c>
-      <c r="P14" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>14</v>
-      </c>
-      <c r="R14" s="4">
-        <v>15</v>
-      </c>
-      <c r="S14" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3</v>
-      </c>
-      <c r="G17" s="1">
-        <v>4</v>
-      </c>
-      <c r="H17" s="1">
-        <v>5</v>
-      </c>
-      <c r="I17" s="1">
-        <v>6</v>
-      </c>
-      <c r="J17" s="1">
-        <v>7</v>
-      </c>
-      <c r="K17" s="1">
-        <v>8</v>
-      </c>
-      <c r="L17" s="1">
-        <v>9</v>
-      </c>
-      <c r="M17" s="1">
-        <v>10</v>
-      </c>
-      <c r="N17" s="1">
-        <v>11</v>
-      </c>
-      <c r="O17" s="1">
-        <v>12</v>
-      </c>
-      <c r="P17" s="1">
-        <v>13</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>14</v>
-      </c>
-      <c r="R17" s="1">
-        <v>15</v>
-      </c>
-      <c r="S17" s="1">
-        <v>16</v>
+      <c r="B17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="1">
         <v>1</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="2" t="s">
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1">
+        <v>7</v>
+      </c>
+      <c r="K21" s="1">
+        <v>8</v>
+      </c>
+      <c r="L21" s="1">
+        <v>9</v>
+      </c>
+      <c r="M21" s="1">
+        <v>10</v>
+      </c>
+      <c r="N21" s="1">
+        <v>11</v>
+      </c>
+      <c r="O21" s="1">
+        <v>12</v>
+      </c>
+      <c r="P21" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>14</v>
+      </c>
+      <c r="R21" s="1">
+        <v>15</v>
+      </c>
+      <c r="S21" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1277,8 +1670,8 @@
     <mergeCell ref="C8:S8"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1294,7 +1687,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1340,7 +1733,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1363,7 +1756,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1409,157 +1802,479 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
+        <v>9</v>
+      </c>
+      <c r="M14" s="4">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4">
+        <v>11</v>
+      </c>
+      <c r="O14" s="4">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>14</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15</v>
+      </c>
+      <c r="S14" s="4">
         <v>16</v>
       </c>
-      <c r="D12" s="4">
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="B15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F17" s="1">
         <v>3</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G17" s="1">
         <v>4</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H17" s="1">
         <v>5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I17" s="1">
         <v>6</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J17" s="1">
         <v>7</v>
       </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="K17" s="1">
+        <v>8</v>
+      </c>
+      <c r="L17" s="1">
         <v>9</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M17" s="1">
         <v>10</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N17" s="1">
         <v>11</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O17" s="1">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P17" s="1">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q17" s="1">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R17" s="1">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S17" s="1">
         <v>16</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1584,56 +2299,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1652,25 +2367,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1693,25 +2408,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1734,25 +2449,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1775,25 +2490,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -1816,25 +2531,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -1857,25 +2572,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -1898,10 +2613,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
@@ -1913,10 +2628,10 @@
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -1939,25 +2654,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -1980,25 +2695,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>43</v>
+        <v>86</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2021,25 +2736,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -2062,25 +2777,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>74</v>
+        <v>92</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -2103,25 +2818,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -2144,25 +2859,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -2185,16 +2900,16 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
@@ -2203,7 +2918,7 @@
         <v>79</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -2226,25 +2941,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -2267,25 +2982,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -2300,88 +3015,6 @@
         <v>8</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="8" t="s">
         <v>8</v>
       </c>
     </row>

--- a/sampleprojects/TaxReturn/excel/states/UT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/UT.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>DT: ut tax</t>
   </si>
@@ -141,6 +141,12 @@
     <t>taxpayer.military_retirement_pay &gt; 0</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
     <t>TC-40A Part 3 code AJ worksheet: taxable military retirement pay times 0.045 (Utah Code 59-10-1043)</t>
   </si>
   <si>
@@ -153,6 +159,9 @@
     <t>No military retirement pay for this taxpayer.</t>
   </si>
   <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -222,7 +231,7 @@
     <t>27320.0</t>
   </si>
   <si>
-    <t>UT taxpayer tax credit phase-out base, head of household: $27,320 for 2025, 1.5 times the single base as every year (TC-40 line 17). Derived from the single figure, not read from the 2025 instructions; confirm when a HOH Utah scenario is written.</t>
+    <t>UT taxpayer tax credit phase-out base, head of household: $27,320 for 2025 (TC-40 line 17; 2025 TC-40 instructions). The credit is reduced by 1.3% of Utah taxable income over this amount.</t>
   </si>
   <si>
     <t>ut_credit_phaseout_joint</t>
@@ -231,7 +240,7 @@
     <t>36426.0</t>
   </si>
   <si>
-    <t>UT taxpayer tax credit phase-out base, married filing jointly or surviving spouse: $36,426 for 2025, twice the single base as every year (TC-40 line 17). Derived from the single figure, not read from the 2025 instructions; confirm when a joint Utah scenario is written.</t>
+    <t>UT taxpayer tax credit phase-out base, married filing jointly or surviving spouse: $36,426 for 2025 (TC-40 line 17; 2025 TC-40 instructions). The credit is reduced by 1.3% of Utah taxable income over this amount.</t>
   </si>
   <si>
     <t>ut_credit_phaseout_rate</t>
@@ -1928,7 +1937,7 @@
         <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>8</v>
@@ -1970,294 +1979,412 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F15" s="4">
         <v>3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G15" s="4">
         <v>4</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I15" s="4">
         <v>6</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J15" s="4">
         <v>7</v>
       </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
         <v>9</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M15" s="4">
         <v>10</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N15" s="4">
         <v>11</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O15" s="4">
         <v>12</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P15" s="4">
         <v>13</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q15" s="4">
         <v>14</v>
       </c>
-      <c r="R14" s="4">
+      <c r="R15" s="4">
         <v>15</v>
       </c>
-      <c r="S14" s="4">
+      <c r="S15" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5">
+    <row r="16">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F18" s="1">
         <v>3</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18" s="1">
         <v>4</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H18" s="1">
         <v>5</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I18" s="1">
         <v>6</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J18" s="1">
         <v>7</v>
       </c>
-      <c r="K17" s="1">
-        <v>8</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
         <v>9</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M18" s="1">
         <v>10</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N18" s="1">
         <v>11</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P18" s="1">
         <v>13</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q18" s="1">
         <v>14</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R18" s="1">
         <v>15</v>
       </c>
-      <c r="S17" s="1">
+      <c r="S18" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
         <v>2</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S19" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2273,8 +2400,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2299,56 +2426,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2367,25 +2494,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -2408,25 +2535,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="H5" s="16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -2449,25 +2576,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2490,25 +2617,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2531,25 +2658,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -2572,25 +2699,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -2613,25 +2740,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2654,25 +2781,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -2695,25 +2822,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2736,25 +2863,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -2777,25 +2904,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -2818,25 +2945,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -2859,25 +2986,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -2900,25 +3027,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -2941,25 +3068,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -2982,25 +3109,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>

--- a/sampleprojects/TaxReturn/excel/states/UT.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/UT.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="ut tax" sheetId="2" r:id="rId4"/>
-    <sheet name="UT Military Retirement Exclusio" sheetId="3" r:id="rId6"/>
+    <sheet name="UT Military Retirement Credit" sheetId="3" r:id="rId6"/>
     <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>DT: ut tax</t>
   </si>
@@ -45,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.ut_tax = 0; set result.ut_state_tax = 0; set result.ut_taxable_income = 0; add "  Utah Tax Calculation (Form TC-40) - flat 4.5%" to job.audit_trail</t>
+    <t>set result.ut_tax = 0; set result.ut_state_tax = 0; set result.ut_taxable_income = 0; set result.ut_base_tax = 0; set result.ut_taxpayer_credit = 0; set result.ut_military_retirement_credit = 0.0; perform UT_Military_Retirement_Credit; set result.ut_taxable_income = the maximum of result.state_calc_agi and 0.0; set result.ut_base_tax = result.ut_taxable_income * ut_tax_rate; add "  Utah Tax Calculation (Form TC-40, 2025) - 4.5% less the taxpayer tax credit and the military retirement credit" to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -54,195 +54,246 @@
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Always compute (UT has no filing-status differences in rate)</t>
+    <t>Married filing jointly or surviving spouse: $36,426 phase-out base</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFJ" or job.filing_status is equal to "QSS"</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Head of household: $27,320 phase-out base</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "HOH"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ACTIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: ACTIONS</t>
+  </si>
+  <si>
+    <t>TC-40 lines 11-20: 6% of (dependent exemptions + federal deduction) less 1.3% of taxable income over $36,426</t>
+  </si>
+  <si>
+    <t>set result.ut_taxpayer_credit = the maximum of ((length of job.dependents * ut_personal_exemption + result.total_deduction) * ut_taxpayer_credit_rate - (the maximum of (result.ut_taxable_income - ut_credit_phaseout_joint) and 0.0) * ut_credit_phaseout_rate) and 0.0</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>TC-40 lines 11-20, head of household base $27,320</t>
+  </si>
+  <si>
+    <t>set result.ut_taxpayer_credit = the maximum of ((length of job.dependents * ut_personal_exemption + result.total_deduction) * ut_taxpayer_credit_rate - (the maximum of (result.ut_taxable_income - ut_credit_phaseout_hoh) and 0.0) * ut_credit_phaseout_rate) and 0.0</t>
+  </si>
+  <si>
+    <t>TC-40 lines 11-20, single/MFS base $18,213</t>
+  </si>
+  <si>
+    <t>set result.ut_taxpayer_credit = the maximum of ((length of job.dependents * ut_personal_exemption + result.total_deduction) * ut_taxpayer_credit_rate - (the maximum of (result.ut_taxable_income - ut_credit_phaseout_single) and 0.0) * ut_credit_phaseout_rate) and 0.0</t>
+  </si>
+  <si>
+    <t>TC-40 line 22 tax less the taxpayer tax credit, line 24 less the military retirement credit (code AJ), not below zero</t>
+  </si>
+  <si>
+    <t>set result.ut_tax = the maximum of (result.ut_base_tax - result.ut_taxpayer_credit - result.ut_military_retirement_credit) and 0.0; set result.ut_state_tax = result.ut_tax; set result.computed_state_taxable_income = result.ut_taxable_income; set result.computed_state_tax = result.ut_tax; add "  UT tax 4.5% of $" + result.ut_taxable_income + " = $" + result.ut_base_tax + "; taxpayer tax credit $" + result.ut_taxpayer_credit + "; military retirement credit $" + result.ut_military_retirement_credit + "; tax $" + result.ut_tax to job.audit_trail</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Utah MFJ/QSS (2025 TC-40): 4.5% of Utah taxable income (federal AGI; the standard deduction and exemptions are not subtracted), less the taxpayer tax credit (6% of the federal deduction plus $2,111 per dependent, phased out at 1.3% of taxable income over $36,426) and the military retirement credit (4.5% of military retirement pay, code AJ).</t>
+  </si>
+  <si>
+    <t>Utah HOH: as above with the $27,320 phase-out base.</t>
+  </si>
+  <si>
+    <t>Utah Single/MFS (2025 TC-40 lines 9-25): 4.5% of taxable income, less the taxpayer tax credit (6% of the federal deduction plus dependent exemptions, less 1.3% of taxable income over $18,213; Utah Code 59-10-1018) and the military retirement credit (Utah Code 59-10-1043).</t>
+  </si>
+  <si>
+    <t>DT: UT Military Retirement Credit</t>
+  </si>
+  <si>
+    <t>COMMENTS: Utah military retirement exclusion. Skeleton — see issue #446. UT allows up to $10,000 exemption on military retirement pay with income caps ($50k Single / $65k MFJ AGI); must choose between military retirement or Social Security exemption.</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 42301</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retirement pay included in AGI</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>TC-40A Part 3 code AJ worksheet: taxable military retirement pay times 0.045 (Utah Code 59-10-1043)</t>
+  </si>
+  <si>
+    <t>add taxpayer.military_retirement_pay * ut_tax_rate to result.ut_military_retirement_credit</t>
+  </si>
+  <si>
+    <t>Military retirement credit, TC-40A Part 3 code AJ: 4.5% of military retirement pay included in AGI, nonrefundable, no carryforward, not with the retirement credit code 18 (Utah Code 59-10-1043; 2025 TC-40 instructions p. 21-22). Utah has no exemption for the pay itself.</t>
+  </si>
+  <si>
+    <t>No military retirement pay for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
+  </si>
+  <si>
+    <t>EDD: EDD</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SubType</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Q Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>(16 attributes)</t>
+  </si>
+  <si>
+    <t>ut_base_tax</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>UT base tax before taxpayer credit (computed)</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_hoh</t>
+  </si>
+  <si>
+    <t>27320.0</t>
+  </si>
+  <si>
+    <t>UT taxpayer tax credit phase-out base, head of household: $27,320 for 2025 (TC-40 line 17; 2025 TC-40 instructions). The credit is reduced by 1.3% of Utah taxable income over this amount.</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_joint</t>
+  </si>
+  <si>
+    <t>36426.0</t>
+  </si>
+  <si>
+    <t>UT taxpayer tax credit phase-out base, married filing jointly or surviving spouse: $36,426 for 2025 (TC-40 line 17; 2025 TC-40 instructions). The credit is reduced by 1.3% of Utah taxable income over this amount.</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_rate</t>
+  </si>
+  <si>
+    <t>0.013</t>
+  </si>
+  <si>
+    <t>UT taxpayer credit phase-out rate 1.3% (2025)</t>
+  </si>
+  <si>
+    <t>ut_credit_phaseout_single</t>
+  </si>
+  <si>
+    <t>18213.0</t>
+  </si>
+  <si>
+    <t>UT taxpayer tax credit phase-out base, single: $18,213 for 2025 (TC-40 line 17; 2025 TC-40 instructions). The credit is reduced by 1.3% of Utah taxable income over this amount.</t>
+  </si>
+  <si>
+    <t>ut_military_retirement_credit</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Utah military retirement credit (computed per taxpayer by UT_Military_Retirement_Credit): a nonrefundable credit of 4.5% (the tax rate) of military retirement pay included in AGI, TC-40A Part 3 code AJ, Utah Code 59-10-1043; cannot be claimed with the retirement credit, code 18 (2025 TC-40 instructions p. 21-22). Utah has no exemption or AGI cap for the pay itself (#1330).</t>
+  </si>
+  <si>
+    <t>ut_military_retirement_taxable</t>
+  </si>
+  <si>
+    <t>UT taxable military retirement after exemption (computed)</t>
+  </si>
+  <si>
+    <t>ut_personal_exemption</t>
+  </si>
+  <si>
+    <t>2111.0</t>
+  </si>
+  <si>
+    <t>UT personal exemption $2,111 per dependent for 2025 (TC-40 line 11; Utah Code 59-10-1018(1)(g)). It is a component of the taxpayer tax credit, not a deduction from taxable income.</t>
+  </si>
+  <si>
+    <t>ut_social_security_exempt</t>
+  </si>
+  <si>
+    <t>boolean</t>
   </si>
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>ACTIONS: COMMENTS</t>
-  </si>
-  <si>
-    <t>DSL: ACTIONS</t>
-  </si>
-  <si>
-    <t>UT taxable income = max(AGI − dependent_exemption × #dependents, 0); tax = 4.5% × taxable_income</t>
-  </si>
-  <si>
-    <t>set result.ut_taxable_income = the maximum of (result.state_calc_agi - length of job.dependents * ut_personal_exemption) and 0.0; set result.ut_tax = result.ut_taxable_income * ut_tax_rate; set result.ut_state_tax = result.ut_tax; add "  UT taxable income (AGI - $2,111 per dependent): $" + result.ut_taxable_income to job.audit_trail; add "  UT state tax (4.5%): $" + result.ut_state_tax to job.audit_trail; set result.computed_state_taxable_income = result.ut_taxable_income; set result.computed_state_tax = result.ut_state_tax</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Policy:</t>
-  </si>
-  <si>
-    <t>Policy Statements</t>
-  </si>
-  <si>
-    <t>UT flat tax: 4.5% × max(AGI − $2,111 × #dependents, 0)</t>
-  </si>
-  <si>
-    <t>DT: UT Military Retirement Exclusion</t>
-  </si>
-  <si>
-    <t>COMMENTS: Utah military retirement exclusion. Skeleton — see issue #446. UT allows up to $10,000 exemption on military retirement pay with income caps ($50k Single / $65k MFJ AGI); must choose between military retirement or Social Security exemption.</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 42301</t>
-  </si>
-  <si>
-    <t>EDD: EDD</t>
-  </si>
-  <si>
-    <t>Entity</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>SubType</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Access</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Collect</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Q Type</t>
-  </si>
-  <si>
-    <t>Options</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(18 attributes)</t>
-  </si>
-  <si>
-    <t>ut_base_tax</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>UT base tax before taxpayer credit (computed)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_hoh</t>
-  </si>
-  <si>
-    <t>23844.0</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out threshold head of household (2025)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_joint</t>
-  </si>
-  <si>
-    <t>31792.0</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out threshold married filing jointly (2025)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_rate</t>
-  </si>
-  <si>
-    <t>0.013</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out rate 1.3% (2025)</t>
-  </si>
-  <si>
-    <t>ut_credit_phaseout_single</t>
-  </si>
-  <si>
-    <t>15896.0</t>
-  </si>
-  <si>
-    <t>UT taxpayer credit phase-out threshold single (2025). Source: Utah State Tax Commission</t>
-  </si>
-  <si>
-    <t>ut_military_exemption_agi_cap_joint</t>
-  </si>
-  <si>
-    <t>65000.0</t>
-  </si>
-  <si>
-    <t>UT military retirement exemption AGI cap joint (2025). Source: MOAA State Report Card</t>
-  </si>
-  <si>
-    <t>ut_military_exemption_agi_cap_single</t>
-  </si>
-  <si>
-    <t>50000.0</t>
-  </si>
-  <si>
-    <t>UT military retirement exemption AGI cap single (2025). Source: MOAA State Report Card</t>
-  </si>
-  <si>
-    <t>ut_military_retirement_exemption</t>
-  </si>
-  <si>
-    <t>10000.0</t>
-  </si>
-  <si>
-    <t>UT military retirement exemption amount (2025). Must choose between this or SS exemption. Source: MOAA State Report Card</t>
-  </si>
-  <si>
-    <t>ut_military_retirement_taxable</t>
-  </si>
-  <si>
-    <t>UT taxable military retirement after exemption (computed)</t>
-  </si>
-  <si>
-    <t>ut_personal_exemption</t>
-  </si>
-  <si>
-    <t>2111.0</t>
-  </si>
-  <si>
-    <t>UT personal exemption per dependent (2025). Source: Utah State Tax Commission</t>
-  </si>
-  <si>
-    <t>ut_social_security_exempt</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
     <t>UT fully exempts Social Security benefits from state income tax (2025). Source: Utah State Tax Commission</t>
   </si>
   <si>
@@ -255,9 +306,6 @@
     <t>ut_state_tax</t>
   </si>
   <si>
-    <t>rw</t>
-  </si>
-  <si>
     <t>UT state income tax (alias for ut_tax)</t>
   </si>
   <si>
@@ -285,7 +333,7 @@
     <t>ut_taxpayer_credit</t>
   </si>
   <si>
-    <t>UT taxpayer tax credit amount (computed)</t>
+    <t>UT taxpayer tax credit (computed): 6% of (federal deduction + $2,111 per dependent), reduced by 1.3% of Utah taxable income over the filing-status base, not below zero (TC-40 lines 11-20; Utah Code 59-10-1018).</t>
   </si>
   <si>
     <t>ut_taxpayer_credit_rate</t>
@@ -988,10 +1036,10 @@
         <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>8</v>
@@ -1033,235 +1081,589 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
         <v>16</v>
       </c>
-      <c r="D14" s="4">
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
-        <v>3</v>
-      </c>
-      <c r="G14" s="4">
-        <v>4</v>
-      </c>
-      <c r="H14" s="4">
-        <v>5</v>
-      </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
-        <v>7</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
-        <v>9</v>
-      </c>
-      <c r="M14" s="4">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4">
-        <v>11</v>
-      </c>
-      <c r="O14" s="4">
-        <v>12</v>
-      </c>
-      <c r="P14" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>14</v>
-      </c>
-      <c r="R14" s="4">
-        <v>15</v>
-      </c>
-      <c r="S14" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3</v>
-      </c>
-      <c r="G17" s="1">
-        <v>4</v>
-      </c>
-      <c r="H17" s="1">
-        <v>5</v>
-      </c>
-      <c r="I17" s="1">
-        <v>6</v>
-      </c>
-      <c r="J17" s="1">
-        <v>7</v>
-      </c>
-      <c r="K17" s="1">
-        <v>8</v>
-      </c>
-      <c r="L17" s="1">
-        <v>9</v>
-      </c>
-      <c r="M17" s="1">
-        <v>10</v>
-      </c>
-      <c r="N17" s="1">
-        <v>11</v>
-      </c>
-      <c r="O17" s="1">
-        <v>12</v>
-      </c>
-      <c r="P17" s="1">
-        <v>13</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>14</v>
-      </c>
-      <c r="R17" s="1">
-        <v>15</v>
-      </c>
-      <c r="S17" s="1">
-        <v>16</v>
+      <c r="B17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="1">
         <v>1</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="2" t="s">
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1">
+        <v>7</v>
+      </c>
+      <c r="K21" s="1">
+        <v>8</v>
+      </c>
+      <c r="L21" s="1">
+        <v>9</v>
+      </c>
+      <c r="M21" s="1">
+        <v>10</v>
+      </c>
+      <c r="N21" s="1">
+        <v>11</v>
+      </c>
+      <c r="O21" s="1">
+        <v>12</v>
+      </c>
+      <c r="P21" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>14</v>
+      </c>
+      <c r="R21" s="1">
+        <v>15</v>
+      </c>
+      <c r="S21" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1277,8 +1679,8 @@
     <mergeCell ref="C8:S8"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1294,7 +1696,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1340,7 +1742,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1363,7 +1765,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1409,157 +1811,597 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
         <v>16</v>
       </c>
-      <c r="D12" s="4">
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F18" s="1">
         <v>3</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G18" s="1">
         <v>4</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H18" s="1">
         <v>5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I18" s="1">
         <v>6</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J18" s="1">
         <v>7</v>
       </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
         <v>9</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M18" s="1">
         <v>10</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N18" s="1">
         <v>11</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P18" s="1">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q18" s="1">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R18" s="1">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S18" s="1">
         <v>16</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1584,56 +2426,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1652,25 +2494,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1693,25 +2535,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1734,25 +2576,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1775,25 +2617,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -1816,25 +2658,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -1857,25 +2699,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -1898,25 +2740,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -1939,25 +2781,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>43</v>
-      </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -1980,25 +2822,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>43</v>
+        <v>89</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>90</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2021,25 +2863,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -2062,25 +2904,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>74</v>
+        <v>95</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -2103,25 +2945,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -2144,25 +2986,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -2185,25 +3027,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -2226,25 +3068,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -2267,25 +3109,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -2300,88 +3142,6 @@
         <v>8</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="8" t="s">
         <v>8</v>
       </c>
     </row>
